--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260412_202610.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260412_202610.xlsx
@@ -4748,7 +4748,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7626,7 +7626,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7762,7 +7762,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260412_202610.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260412_202610.xlsx
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7626,7 +7626,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7762,7 +7762,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260412_202610.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260412_202610.xlsx
@@ -4748,7 +4748,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7626,7 +7626,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7762,7 +7762,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260412_202610.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260412_202610.xlsx
@@ -4748,7 +4748,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260412_202610.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260412_202610.xlsx
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7626,7 +7626,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7762,7 +7762,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260412_202610.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260412_202610.xlsx
@@ -4748,7 +4748,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7626,7 +7626,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7762,7 +7762,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260412_202610.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260412_202610.xlsx
@@ -4748,7 +4748,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7626,7 +7626,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7762,7 +7762,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260412_202610.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260412_202610.xlsx
@@ -4748,7 +4748,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7626,7 +7626,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7762,7 +7762,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260412_202610.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260412_202610.xlsx
@@ -4748,7 +4748,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7626,7 +7626,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7762,7 +7762,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260412_202610.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260412_202610.xlsx
@@ -4748,7 +4748,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260412_202610.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260412_202610.xlsx
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260412_202610.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260412_202610.xlsx
@@ -4748,7 +4748,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260412_202610.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260412_202610.xlsx
@@ -4748,7 +4748,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7626,7 +7626,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7762,7 +7762,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260412_202610.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260412_202610.xlsx
@@ -4748,7 +4748,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7626,7 +7626,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7762,7 +7762,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260412_202610.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260412_202610.xlsx
@@ -4748,7 +4748,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260412_202610.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260412_202610.xlsx
@@ -4748,7 +4748,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260412_202610.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260412_202610.xlsx
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260412_202610.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260412_202610.xlsx
@@ -7626,7 +7626,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7762,7 +7762,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260412_202610.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260412_202610.xlsx
@@ -4748,7 +4748,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260412_202610.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260412_202610.xlsx
@@ -7626,7 +7626,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7762,7 +7762,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260412_202610.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260412_202610.xlsx
@@ -4748,7 +4748,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7626,7 +7626,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7762,7 +7762,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260412_202610.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260412_202610.xlsx
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7626,7 +7626,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7762,7 +7762,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260412_202610.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260412_202610.xlsx
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7626,7 +7626,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7762,7 +7762,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260412_202610.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260412_202610.xlsx
@@ -4748,7 +4748,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7626,7 +7626,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7762,7 +7762,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
